--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>81004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R16" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,11 +2200,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B17" t="n">
-        <v>81004</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R17" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2301,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156513</v>
+        <v>128156494</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483695</v>
+        <v>483844</v>
       </c>
       <c r="R2" t="n">
-        <v>6950029</v>
+        <v>6949850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156494</v>
+        <v>128156513</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>91351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483844</v>
+        <v>483695</v>
       </c>
       <c r="R3" t="n">
-        <v>6949850</v>
+        <v>6950029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B4" t="n">
-        <v>80133</v>
+        <v>80036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R4" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B5" t="n">
-        <v>80036</v>
+        <v>80133</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R5" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1301,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156495</v>
+        <v>128156500</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>91925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R8" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,32 +1402,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156501</v>
+        <v>128156495</v>
       </c>
       <c r="B9" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483832</v>
+        <v>483870</v>
       </c>
       <c r="R9" t="n">
-        <v>6949887</v>
+        <v>6949710</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,6 +1473,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156500</v>
+        <v>128156501</v>
       </c>
       <c r="B10" t="n">
-        <v>91924</v>
+        <v>80161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483706</v>
+        <v>483832</v>
       </c>
       <c r="R10" t="n">
-        <v>6949897</v>
+        <v>6949887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156516</v>
+        <v>128156511</v>
       </c>
       <c r="B13" t="n">
-        <v>80132</v>
+        <v>80098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483708</v>
+        <v>483692</v>
       </c>
       <c r="R13" t="n">
-        <v>6949974</v>
+        <v>6949854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,11 +1887,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,32 +1917,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128156508</v>
+        <v>128156516</v>
       </c>
       <c r="B14" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483701</v>
+        <v>483708</v>
       </c>
       <c r="R14" t="n">
-        <v>6949917</v>
+        <v>6949974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,10 +2023,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156511</v>
+        <v>128156508</v>
       </c>
       <c r="B15" t="n">
-        <v>80098</v>
+        <v>80161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,21 +2034,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483692</v>
+        <v>483701</v>
       </c>
       <c r="R15" t="n">
-        <v>6949854</v>
+        <v>6949917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2094,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156494</v>
+        <v>128156513</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483844</v>
+        <v>483695</v>
       </c>
       <c r="R2" t="n">
-        <v>6949850</v>
+        <v>6950029</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,11 +748,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156513</v>
+        <v>128156494</v>
       </c>
       <c r="B3" t="n">
-        <v>91351</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483695</v>
+        <v>483844</v>
       </c>
       <c r="R3" t="n">
-        <v>6950029</v>
+        <v>6949850</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,6 +849,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -871,7 +871,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1304,7 +1304,7 @@
         <v>128156500</v>
       </c>
       <c r="B8" t="n">
-        <v>91925</v>
+        <v>91926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156511</v>
+        <v>128156516</v>
       </c>
       <c r="B13" t="n">
-        <v>80098</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483692</v>
+        <v>483708</v>
       </c>
       <c r="R13" t="n">
-        <v>6949854</v>
+        <v>6949974</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,6 +1889,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1906,7 +1911,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1917,32 +1922,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128156516</v>
+        <v>128156508</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483708</v>
+        <v>483701</v>
       </c>
       <c r="R14" t="n">
-        <v>6949974</v>
+        <v>6949917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,7 +2017,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2023,10 +2028,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156508</v>
+        <v>128156511</v>
       </c>
       <c r="B15" t="n">
-        <v>80161</v>
+        <v>80098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,21 +2039,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483701</v>
+        <v>483692</v>
       </c>
       <c r="R15" t="n">
-        <v>6949917</v>
+        <v>6949854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,11 +2101,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B16" t="n">
-        <v>81004</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R16" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,6 +2202,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2219,7 +2224,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>81004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R17" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2303,11 +2308,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B4" t="n">
-        <v>80036</v>
+        <v>80133</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R4" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B5" t="n">
-        <v>80133</v>
+        <v>80036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R5" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156498</v>
+        <v>128156500</v>
       </c>
       <c r="B7" t="n">
-        <v>80133</v>
+        <v>91926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156500</v>
+        <v>128156498</v>
       </c>
       <c r="B8" t="n">
-        <v>91926</v>
+        <v>80133</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156516</v>
+        <v>128156511</v>
       </c>
       <c r="B13" t="n">
-        <v>80132</v>
+        <v>80098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483708</v>
+        <v>483692</v>
       </c>
       <c r="R13" t="n">
-        <v>6949974</v>
+        <v>6949854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,11 +1887,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2023,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156511</v>
+        <v>128156516</v>
       </c>
       <c r="B15" t="n">
-        <v>80098</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483692</v>
+        <v>483708</v>
       </c>
       <c r="R15" t="n">
-        <v>6949854</v>
+        <v>6949974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2094,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>81004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R16" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,11 +2200,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B17" t="n">
-        <v>81004</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R17" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2301,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B4" t="n">
-        <v>80133</v>
+        <v>80036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R4" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B5" t="n">
-        <v>80036</v>
+        <v>80133</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R5" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B16" t="n">
-        <v>81004</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R16" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2200,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>81004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R17" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B4" t="n">
-        <v>80036</v>
+        <v>80133</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R4" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B5" t="n">
-        <v>80133</v>
+        <v>80036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R5" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B4" t="n">
-        <v>80133</v>
+        <v>80036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R4" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B5" t="n">
-        <v>80036</v>
+        <v>80133</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R5" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156511</v>
+        <v>128156516</v>
       </c>
       <c r="B13" t="n">
-        <v>80098</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483692</v>
+        <v>483708</v>
       </c>
       <c r="R13" t="n">
-        <v>6949854</v>
+        <v>6949974</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156516</v>
+        <v>128156511</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>80098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483708</v>
+        <v>483692</v>
       </c>
       <c r="R15" t="n">
-        <v>6949974</v>
+        <v>6949854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B16" t="n">
-        <v>81004</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R16" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2200,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>81004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R17" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156500</v>
+        <v>128156498</v>
       </c>
       <c r="B7" t="n">
-        <v>91926</v>
+        <v>80133</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156498</v>
+        <v>128156495</v>
       </c>
       <c r="B8" t="n">
-        <v>80133</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483706</v>
+        <v>483870</v>
       </c>
       <c r="R8" t="n">
-        <v>6949897</v>
+        <v>6949710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1372,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,32 +1407,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156495</v>
+        <v>128156501</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483870</v>
+        <v>483832</v>
       </c>
       <c r="R9" t="n">
-        <v>6949710</v>
+        <v>6949887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,11 +1478,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156501</v>
+        <v>128156500</v>
       </c>
       <c r="B10" t="n">
-        <v>80161</v>
+        <v>91926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483832</v>
+        <v>483706</v>
       </c>
       <c r="R10" t="n">
-        <v>6949887</v>
+        <v>6949897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156516</v>
+        <v>128156511</v>
       </c>
       <c r="B13" t="n">
-        <v>80132</v>
+        <v>80098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483708</v>
+        <v>483692</v>
       </c>
       <c r="R13" t="n">
-        <v>6949974</v>
+        <v>6949854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,11 +1887,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2023,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156511</v>
+        <v>128156516</v>
       </c>
       <c r="B15" t="n">
-        <v>80098</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483692</v>
+        <v>483708</v>
       </c>
       <c r="R15" t="n">
-        <v>6949854</v>
+        <v>6949974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2094,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128156513</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>128156494</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B4" t="n">
-        <v>80036</v>
+        <v>80136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R4" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B5" t="n">
-        <v>80133</v>
+        <v>80039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R5" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1097,7 +1097,7 @@
         <v>128156509</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156498</v>
+        <v>128156495</v>
       </c>
       <c r="B7" t="n">
-        <v>80133</v>
+        <v>80135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483706</v>
+        <v>483870</v>
       </c>
       <c r="R7" t="n">
-        <v>6949897</v>
+        <v>6949710</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,6 +1273,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1301,32 +1306,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156495</v>
+        <v>128156501</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>80164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483870</v>
+        <v>483832</v>
       </c>
       <c r="R8" t="n">
-        <v>6949710</v>
+        <v>6949887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,11 +1379,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1407,32 +1407,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156501</v>
+        <v>128156498</v>
       </c>
       <c r="B9" t="n">
-        <v>80161</v>
+        <v>80136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483832</v>
+        <v>483706</v>
       </c>
       <c r="R9" t="n">
-        <v>6949887</v>
+        <v>6949897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>128156500</v>
       </c>
       <c r="B10" t="n">
-        <v>91926</v>
+        <v>91934</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1609,32 +1609,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128156503</v>
+        <v>128156514</v>
       </c>
       <c r="B11" t="n">
-        <v>80168</v>
+        <v>80135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483690</v>
+        <v>483829</v>
       </c>
       <c r="R11" t="n">
-        <v>6949852</v>
+        <v>6949915</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,11 +1682,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1704,7 +1699,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1715,32 +1710,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128156514</v>
+        <v>128156503</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>80171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483829</v>
+        <v>483690</v>
       </c>
       <c r="R12" t="n">
-        <v>6949915</v>
+        <v>6949852</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1783,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1819,7 +1819,7 @@
         <v>128156511</v>
       </c>
       <c r="B13" t="n">
-        <v>80098</v>
+        <v>80101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1920,7 +1920,7 @@
         <v>128156508</v>
       </c>
       <c r="B14" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2026,7 +2026,7 @@
         <v>128156516</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>81007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R16" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,11 +2202,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2224,7 +2219,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2235,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B17" t="n">
-        <v>81004</v>
+        <v>80135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R17" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,6 +2303,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2339,7 +2339,7 @@
         <v>128156496</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2445,7 +2445,7 @@
         <v>128156515</v>
       </c>
       <c r="B19" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2546,7 +2546,7 @@
         <v>128156499</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2647,7 +2647,7 @@
         <v>128156517</v>
       </c>
       <c r="B21" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2753,7 +2753,7 @@
         <v>128156510</v>
       </c>
       <c r="B22" t="n">
-        <v>81004</v>
+        <v>81007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156513</v>
+        <v>128156494</v>
       </c>
       <c r="B2" t="n">
-        <v>91360</v>
+        <v>80188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483695</v>
+        <v>483844</v>
       </c>
       <c r="R2" t="n">
-        <v>6950029</v>
+        <v>6949850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156494</v>
+        <v>128156513</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>91452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483844</v>
+        <v>483695</v>
       </c>
       <c r="R3" t="n">
-        <v>6949850</v>
+        <v>6950029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>128156507</v>
       </c>
       <c r="B4" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128156502</v>
       </c>
       <c r="B5" t="n">
-        <v>80039</v>
+        <v>80092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>128156509</v>
       </c>
       <c r="B6" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156495</v>
+        <v>128156500</v>
       </c>
       <c r="B7" t="n">
-        <v>80135</v>
+        <v>92026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R7" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156501</v>
+        <v>128156498</v>
       </c>
       <c r="B8" t="n">
-        <v>80164</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483832</v>
+        <v>483706</v>
       </c>
       <c r="R8" t="n">
-        <v>6949887</v>
+        <v>6949897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156498</v>
+        <v>128156495</v>
       </c>
       <c r="B9" t="n">
-        <v>80136</v>
+        <v>80188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,21 +1413,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483706</v>
+        <v>483870</v>
       </c>
       <c r="R9" t="n">
-        <v>6949897</v>
+        <v>6949710</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,6 +1473,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156500</v>
+        <v>128156501</v>
       </c>
       <c r="B10" t="n">
-        <v>91934</v>
+        <v>80217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483706</v>
+        <v>483832</v>
       </c>
       <c r="R10" t="n">
-        <v>6949897</v>
+        <v>6949887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,32 +1609,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128156514</v>
+        <v>128156503</v>
       </c>
       <c r="B11" t="n">
-        <v>80135</v>
+        <v>80224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483829</v>
+        <v>483690</v>
       </c>
       <c r="R11" t="n">
-        <v>6949915</v>
+        <v>6949852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,6 +1680,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,32 +1715,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128156503</v>
+        <v>128156514</v>
       </c>
       <c r="B12" t="n">
-        <v>80171</v>
+        <v>80188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483690</v>
+        <v>483829</v>
       </c>
       <c r="R12" t="n">
-        <v>6949852</v>
+        <v>6949915</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156511</v>
+        <v>128156516</v>
       </c>
       <c r="B13" t="n">
-        <v>80101</v>
+        <v>80188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483692</v>
+        <v>483708</v>
       </c>
       <c r="R13" t="n">
-        <v>6949854</v>
+        <v>6949974</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,7 +1925,7 @@
         <v>128156508</v>
       </c>
       <c r="B14" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156516</v>
+        <v>128156511</v>
       </c>
       <c r="B15" t="n">
-        <v>80135</v>
+        <v>80154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483708</v>
+        <v>483692</v>
       </c>
       <c r="R15" t="n">
-        <v>6949974</v>
+        <v>6949854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B16" t="n">
-        <v>81007</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R16" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2200,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B17" t="n">
-        <v>80135</v>
+        <v>81068</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R17" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,7 +2339,7 @@
         <v>128156496</v>
       </c>
       <c r="B18" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>128156515</v>
       </c>
       <c r="B19" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>128156499</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128156517</v>
       </c>
       <c r="B21" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>128156510</v>
       </c>
       <c r="B22" t="n">
-        <v>81007</v>
+        <v>81068</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156494</v>
+        <v>128156513</v>
       </c>
       <c r="B2" t="n">
-        <v>80188</v>
+        <v>91452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483844</v>
+        <v>483695</v>
       </c>
       <c r="R2" t="n">
-        <v>6949850</v>
+        <v>6950029</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156513</v>
+        <v>128156494</v>
       </c>
       <c r="B3" t="n">
-        <v>91452</v>
+        <v>80188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483695</v>
+        <v>483844</v>
       </c>
       <c r="R3" t="n">
-        <v>6950029</v>
+        <v>6949850</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156500</v>
+        <v>128156498</v>
       </c>
       <c r="B7" t="n">
-        <v>92026</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156498</v>
+        <v>128156501</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>80217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483706</v>
+        <v>483832</v>
       </c>
       <c r="R8" t="n">
-        <v>6949897</v>
+        <v>6949887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,32 +1402,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156495</v>
+        <v>128156500</v>
       </c>
       <c r="B9" t="n">
-        <v>80188</v>
+        <v>92026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R9" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,11 +1473,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,32 +1503,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156501</v>
+        <v>128156495</v>
       </c>
       <c r="B10" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483832</v>
+        <v>483870</v>
       </c>
       <c r="R10" t="n">
-        <v>6949887</v>
+        <v>6949710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,6 +1574,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>81068</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R16" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,11 +2200,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B17" t="n">
-        <v>81068</v>
+        <v>80188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R17" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2301,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B4" t="n">
-        <v>80189</v>
+        <v>80092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R4" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B5" t="n">
-        <v>80092</v>
+        <v>80189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R5" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1301,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156501</v>
+        <v>128156495</v>
       </c>
       <c r="B8" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483832</v>
+        <v>483870</v>
       </c>
       <c r="R8" t="n">
-        <v>6949887</v>
+        <v>6949710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1374,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1391,7 +1396,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1402,32 +1407,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156500</v>
+        <v>128156501</v>
       </c>
       <c r="B9" t="n">
-        <v>92026</v>
+        <v>80217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483706</v>
+        <v>483832</v>
       </c>
       <c r="R9" t="n">
-        <v>6949897</v>
+        <v>6949887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,7 +1497,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1503,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156495</v>
+        <v>128156500</v>
       </c>
       <c r="B10" t="n">
-        <v>80188</v>
+        <v>92026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R10" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,11 +1581,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156498</v>
+        <v>128156500</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>92026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156495</v>
+        <v>128156498</v>
       </c>
       <c r="B8" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R8" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,32 +1402,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156501</v>
+        <v>128156495</v>
       </c>
       <c r="B9" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483832</v>
+        <v>483870</v>
       </c>
       <c r="R9" t="n">
-        <v>6949887</v>
+        <v>6949710</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,6 +1473,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156500</v>
+        <v>128156501</v>
       </c>
       <c r="B10" t="n">
-        <v>92026</v>
+        <v>80217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483706</v>
+        <v>483832</v>
       </c>
       <c r="R10" t="n">
-        <v>6949897</v>
+        <v>6949887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B16" t="n">
-        <v>81068</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R16" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2200,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B17" t="n">
-        <v>80188</v>
+        <v>81068</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R17" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156513</v>
+        <v>128156494</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>80192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483695</v>
+        <v>483844</v>
       </c>
       <c r="R2" t="n">
-        <v>6950029</v>
+        <v>6949850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156494</v>
+        <v>128156513</v>
       </c>
       <c r="B3" t="n">
-        <v>80188</v>
+        <v>91464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483844</v>
+        <v>483695</v>
       </c>
       <c r="R3" t="n">
-        <v>6949850</v>
+        <v>6950029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B4" t="n">
-        <v>80092</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R4" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B5" t="n">
-        <v>80189</v>
+        <v>80096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R5" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1097,7 @@
         <v>128156509</v>
       </c>
       <c r="B6" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156500</v>
+        <v>128156498</v>
       </c>
       <c r="B7" t="n">
-        <v>92026</v>
+        <v>80193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156498</v>
+        <v>128156495</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483706</v>
+        <v>483870</v>
       </c>
       <c r="R8" t="n">
-        <v>6949897</v>
+        <v>6949710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1372,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,32 +1407,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156495</v>
+        <v>128156501</v>
       </c>
       <c r="B9" t="n">
-        <v>80188</v>
+        <v>80221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483870</v>
+        <v>483832</v>
       </c>
       <c r="R9" t="n">
-        <v>6949710</v>
+        <v>6949887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,11 +1478,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156501</v>
+        <v>128156500</v>
       </c>
       <c r="B10" t="n">
-        <v>80217</v>
+        <v>92038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483832</v>
+        <v>483706</v>
       </c>
       <c r="R10" t="n">
-        <v>6949887</v>
+        <v>6949897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
         <v>128156503</v>
       </c>
       <c r="B11" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>128156514</v>
       </c>
       <c r="B12" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156516</v>
+        <v>128156511</v>
       </c>
       <c r="B13" t="n">
-        <v>80188</v>
+        <v>80158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483708</v>
+        <v>483692</v>
       </c>
       <c r="R13" t="n">
-        <v>6949974</v>
+        <v>6949854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,11 +1887,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,32 +1917,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128156508</v>
+        <v>128156516</v>
       </c>
       <c r="B14" t="n">
-        <v>80217</v>
+        <v>80192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483701</v>
+        <v>483708</v>
       </c>
       <c r="R14" t="n">
-        <v>6949917</v>
+        <v>6949974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,10 +2023,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156511</v>
+        <v>128156508</v>
       </c>
       <c r="B15" t="n">
-        <v>80154</v>
+        <v>80221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,21 +2034,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483692</v>
+        <v>483701</v>
       </c>
       <c r="R15" t="n">
-        <v>6949854</v>
+        <v>6949917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2094,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,7 +2132,7 @@
         <v>128156504</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>128156506</v>
       </c>
       <c r="B17" t="n">
-        <v>81068</v>
+        <v>81072</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128156496</v>
       </c>
       <c r="B18" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>128156515</v>
       </c>
       <c r="B19" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>128156499</v>
       </c>
       <c r="B20" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>128156517</v>
       </c>
       <c r="B21" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>128156510</v>
       </c>
       <c r="B22" t="n">
-        <v>81068</v>
+        <v>81072</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156494</v>
+        <v>128156513</v>
       </c>
       <c r="B2" t="n">
-        <v>80192</v>
+        <v>91464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483844</v>
+        <v>483695</v>
       </c>
       <c r="R2" t="n">
-        <v>6949850</v>
+        <v>6950029</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156513</v>
+        <v>128156494</v>
       </c>
       <c r="B3" t="n">
-        <v>91464</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483695</v>
+        <v>483844</v>
       </c>
       <c r="R3" t="n">
-        <v>6950029</v>
+        <v>6949850</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156498</v>
+        <v>128156495</v>
       </c>
       <c r="B7" t="n">
-        <v>80193</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483706</v>
+        <v>483870</v>
       </c>
       <c r="R7" t="n">
-        <v>6949897</v>
+        <v>6949710</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,32 +1306,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156495</v>
+        <v>128156501</v>
       </c>
       <c r="B8" t="n">
-        <v>80192</v>
+        <v>80221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483870</v>
+        <v>483832</v>
       </c>
       <c r="R8" t="n">
-        <v>6949710</v>
+        <v>6949887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,11 +1377,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,32 +1407,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156501</v>
+        <v>128156500</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>92038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483832</v>
+        <v>483706</v>
       </c>
       <c r="R9" t="n">
-        <v>6949887</v>
+        <v>6949897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156500</v>
+        <v>128156498</v>
       </c>
       <c r="B10" t="n">
-        <v>92038</v>
+        <v>80193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156511</v>
+        <v>128156516</v>
       </c>
       <c r="B13" t="n">
-        <v>80158</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483692</v>
+        <v>483708</v>
       </c>
       <c r="R13" t="n">
-        <v>6949854</v>
+        <v>6949974</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,32 +1922,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128156516</v>
+        <v>128156508</v>
       </c>
       <c r="B14" t="n">
-        <v>80192</v>
+        <v>80221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483708</v>
+        <v>483701</v>
       </c>
       <c r="R14" t="n">
-        <v>6949974</v>
+        <v>6949917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2023,10 +2028,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156508</v>
+        <v>128156511</v>
       </c>
       <c r="B15" t="n">
-        <v>80221</v>
+        <v>80158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,21 +2039,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483701</v>
+        <v>483692</v>
       </c>
       <c r="R15" t="n">
-        <v>6949917</v>
+        <v>6949854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128156513</v>
       </c>
       <c r="B2" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>128156494</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -885,7 +885,7 @@
         <v>128156507</v>
       </c>
       <c r="B4" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -991,7 +991,7 @@
         <v>128156502</v>
       </c>
       <c r="B5" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1097,7 +1097,7 @@
         <v>128156509</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156495</v>
+        <v>128156498</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>80195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R7" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,11 +1273,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1306,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156501</v>
+        <v>128156495</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483832</v>
+        <v>483870</v>
       </c>
       <c r="R8" t="n">
-        <v>6949887</v>
+        <v>6949710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,6 +1374,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1407,32 +1407,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156500</v>
+        <v>128156501</v>
       </c>
       <c r="B9" t="n">
-        <v>92038</v>
+        <v>80223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483706</v>
+        <v>483832</v>
       </c>
       <c r="R9" t="n">
-        <v>6949897</v>
+        <v>6949887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156498</v>
+        <v>128156500</v>
       </c>
       <c r="B10" t="n">
-        <v>80193</v>
+        <v>92040</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1612,7 +1612,7 @@
         <v>128156503</v>
       </c>
       <c r="B11" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1718,7 +1718,7 @@
         <v>128156514</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1816,32 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156516</v>
+        <v>128156511</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>80160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483708</v>
+        <v>483692</v>
       </c>
       <c r="R13" t="n">
-        <v>6949974</v>
+        <v>6949854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,11 +1889,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1911,7 +1906,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1922,32 +1917,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128156508</v>
+        <v>128156516</v>
       </c>
       <c r="B14" t="n">
-        <v>80221</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483701</v>
+        <v>483708</v>
       </c>
       <c r="R14" t="n">
-        <v>6949917</v>
+        <v>6949974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2017,7 +2012,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2028,10 +2023,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156511</v>
+        <v>128156508</v>
       </c>
       <c r="B15" t="n">
-        <v>80158</v>
+        <v>80223</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,21 +2034,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483692</v>
+        <v>483701</v>
       </c>
       <c r="R15" t="n">
-        <v>6949854</v>
+        <v>6949917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,6 +2096,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2132,7 +2132,7 @@
         <v>128156504</v>
       </c>
       <c r="B16" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2238,7 +2238,7 @@
         <v>128156506</v>
       </c>
       <c r="B17" t="n">
-        <v>81072</v>
+        <v>81074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2339,7 +2339,7 @@
         <v>128156496</v>
       </c>
       <c r="B18" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2445,7 +2445,7 @@
         <v>128156515</v>
       </c>
       <c r="B19" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2546,7 +2546,7 @@
         <v>128156499</v>
       </c>
       <c r="B20" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2647,7 +2647,7 @@
         <v>128156517</v>
       </c>
       <c r="B21" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2753,7 +2753,7 @@
         <v>128156510</v>
       </c>
       <c r="B22" t="n">
-        <v>81072</v>
+        <v>81074</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156513</v>
+        <v>128156494</v>
       </c>
       <c r="B2" t="n">
-        <v>91466</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483695</v>
+        <v>483844</v>
       </c>
       <c r="R2" t="n">
-        <v>6950029</v>
+        <v>6949850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156494</v>
+        <v>128156513</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>91466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483844</v>
+        <v>483695</v>
       </c>
       <c r="R3" t="n">
-        <v>6949850</v>
+        <v>6950029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B4" t="n">
-        <v>80195</v>
+        <v>80098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R4" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B5" t="n">
-        <v>80098</v>
+        <v>80195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R5" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156498</v>
+        <v>128156500</v>
       </c>
       <c r="B7" t="n">
-        <v>80195</v>
+        <v>92040</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156495</v>
+        <v>128156498</v>
       </c>
       <c r="B8" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R8" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,32 +1402,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156501</v>
+        <v>128156495</v>
       </c>
       <c r="B9" t="n">
-        <v>80223</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483832</v>
+        <v>483870</v>
       </c>
       <c r="R9" t="n">
-        <v>6949887</v>
+        <v>6949710</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,6 +1473,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156500</v>
+        <v>128156501</v>
       </c>
       <c r="B10" t="n">
-        <v>92040</v>
+        <v>80223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483706</v>
+        <v>483832</v>
       </c>
       <c r="R10" t="n">
-        <v>6949897</v>
+        <v>6949887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,32 +1609,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128156503</v>
+        <v>128156514</v>
       </c>
       <c r="B11" t="n">
-        <v>80230</v>
+        <v>80194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483690</v>
+        <v>483829</v>
       </c>
       <c r="R11" t="n">
-        <v>6949852</v>
+        <v>6949915</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,11 +1680,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,32 +1710,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128156514</v>
+        <v>128156503</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>80230</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483829</v>
+        <v>483690</v>
       </c>
       <c r="R12" t="n">
-        <v>6949915</v>
+        <v>6949852</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>81074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R16" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,11 +2200,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B17" t="n">
-        <v>81074</v>
+        <v>80194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R17" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2301,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B16" t="n">
-        <v>81074</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R16" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2200,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B17" t="n">
-        <v>80194</v>
+        <v>81074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R17" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156494</v>
+        <v>128156513</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>91467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483844</v>
+        <v>483695</v>
       </c>
       <c r="R2" t="n">
-        <v>6949850</v>
+        <v>6950029</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156513</v>
+        <v>128156494</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483695</v>
+        <v>483844</v>
       </c>
       <c r="R3" t="n">
-        <v>6950029</v>
+        <v>6949850</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B4" t="n">
-        <v>80098</v>
+        <v>80195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R4" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B5" t="n">
-        <v>80195</v>
+        <v>80098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R5" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156500</v>
+        <v>128156501</v>
       </c>
       <c r="B7" t="n">
-        <v>92040</v>
+        <v>80223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483706</v>
+        <v>483832</v>
       </c>
       <c r="R7" t="n">
-        <v>6949897</v>
+        <v>6949887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156498</v>
+        <v>128156495</v>
       </c>
       <c r="B8" t="n">
-        <v>80195</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483706</v>
+        <v>483870</v>
       </c>
       <c r="R8" t="n">
-        <v>6949897</v>
+        <v>6949710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1372,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156495</v>
+        <v>128156498</v>
       </c>
       <c r="B9" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R9" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,11 +1478,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,32 +1508,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156501</v>
+        <v>128156500</v>
       </c>
       <c r="B10" t="n">
-        <v>80223</v>
+        <v>92041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483832</v>
+        <v>483706</v>
       </c>
       <c r="R10" t="n">
-        <v>6949887</v>
+        <v>6949897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,32 +1609,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128156514</v>
+        <v>128156503</v>
       </c>
       <c r="B11" t="n">
-        <v>80194</v>
+        <v>80230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483829</v>
+        <v>483690</v>
       </c>
       <c r="R11" t="n">
-        <v>6949915</v>
+        <v>6949852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,6 +1680,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,32 +1715,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128156503</v>
+        <v>128156514</v>
       </c>
       <c r="B12" t="n">
-        <v>80230</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483690</v>
+        <v>483829</v>
       </c>
       <c r="R12" t="n">
-        <v>6949852</v>
+        <v>6949915</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156511</v>
+        <v>128156508</v>
       </c>
       <c r="B13" t="n">
-        <v>80160</v>
+        <v>80223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483692</v>
+        <v>483701</v>
       </c>
       <c r="R13" t="n">
-        <v>6949854</v>
+        <v>6949917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2028,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156508</v>
+        <v>128156511</v>
       </c>
       <c r="B15" t="n">
-        <v>80223</v>
+        <v>80160</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,21 +2039,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483701</v>
+        <v>483692</v>
       </c>
       <c r="R15" t="n">
-        <v>6949917</v>
+        <v>6949854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -882,32 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156507</v>
+        <v>128156502</v>
       </c>
       <c r="B4" t="n">
-        <v>80195</v>
+        <v>80098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483701</v>
+        <v>483690</v>
       </c>
       <c r="R4" t="n">
-        <v>6949917</v>
+        <v>6949852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156502</v>
+        <v>128156507</v>
       </c>
       <c r="B5" t="n">
-        <v>80098</v>
+        <v>80195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483690</v>
+        <v>483701</v>
       </c>
       <c r="R5" t="n">
-        <v>6949852</v>
+        <v>6949917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov asp.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1301,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156495</v>
+        <v>128156500</v>
       </c>
       <c r="B8" t="n">
-        <v>80194</v>
+        <v>92041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483870</v>
+        <v>483706</v>
       </c>
       <c r="R8" t="n">
-        <v>6949710</v>
+        <v>6949897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,32 +1503,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156500</v>
+        <v>128156495</v>
       </c>
       <c r="B10" t="n">
-        <v>92041</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483706</v>
+        <v>483870</v>
       </c>
       <c r="R10" t="n">
-        <v>6949897</v>
+        <v>6949710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,6 +1574,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156504</v>
+        <v>128156506</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>81074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483690</v>
+        <v>483764</v>
       </c>
       <c r="R16" t="n">
-        <v>6949852</v>
+        <v>6949936</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,11 +2200,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156506</v>
+        <v>128156504</v>
       </c>
       <c r="B17" t="n">
-        <v>81074</v>
+        <v>80194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483764</v>
+        <v>483690</v>
       </c>
       <c r="R17" t="n">
-        <v>6949936</v>
+        <v>6949852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2301,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128156513</v>
+        <v>128156500</v>
       </c>
       <c r="B2" t="n">
-        <v>91467</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483695</v>
+        <v>483706</v>
       </c>
       <c r="R2" t="n">
-        <v>6950029</v>
+        <v>6949897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128156494</v>
+        <v>128156506</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483844</v>
+        <v>483764</v>
       </c>
       <c r="R3" t="n">
-        <v>6949850</v>
+        <v>6949936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +847,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128156502</v>
+        <v>128156510</v>
       </c>
       <c r="B4" t="n">
-        <v>80098</v>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483690</v>
+        <v>483849</v>
       </c>
       <c r="R4" t="n">
-        <v>6949852</v>
+        <v>6949856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128156507</v>
+        <v>128156513</v>
       </c>
       <c r="B5" t="n">
-        <v>80195</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483701</v>
+        <v>483695</v>
       </c>
       <c r="R5" t="n">
-        <v>6949917</v>
+        <v>6950029</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,11 +1049,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128156509</v>
+        <v>128156498</v>
       </c>
       <c r="B6" t="n">
-        <v>80194</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483701</v>
+        <v>483706</v>
       </c>
       <c r="R6" t="n">
-        <v>6949917</v>
+        <v>6949897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,11 +1150,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128156501</v>
+        <v>128156507</v>
       </c>
       <c r="B7" t="n">
-        <v>80223</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483832</v>
+        <v>483701</v>
       </c>
       <c r="R7" t="n">
-        <v>6949887</v>
+        <v>6949917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,32 +1286,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128156500</v>
+        <v>128156515</v>
       </c>
       <c r="B8" t="n">
-        <v>92041</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483706</v>
+        <v>483695</v>
       </c>
       <c r="R8" t="n">
-        <v>6949897</v>
+        <v>6949873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128156498</v>
+        <v>128156517</v>
       </c>
       <c r="B9" t="n">
-        <v>80195</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483706</v>
+        <v>483708</v>
       </c>
       <c r="R9" t="n">
-        <v>6949897</v>
+        <v>6949974</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,6 +1458,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,32 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128156495</v>
+        <v>128156505</v>
       </c>
       <c r="B10" t="n">
-        <v>80194</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483870</v>
+        <v>483938</v>
       </c>
       <c r="R10" t="n">
-        <v>6949710</v>
+        <v>6949657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,7 +1568,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128156503</v>
+        <v>128156502</v>
       </c>
       <c r="B11" t="n">
-        <v>80230</v>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128156514</v>
+        <v>128156512</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483829</v>
+        <v>483714</v>
       </c>
       <c r="R12" t="n">
-        <v>6949915</v>
+        <v>6950034</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,45 +1806,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128156508</v>
+        <v>103968142</v>
       </c>
       <c r="B13" t="n">
-        <v>80223</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Näktesbergen, Jmt</t>
+          <t>Skäftesmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483701</v>
+        <v>483563</v>
       </c>
       <c r="R13" t="n">
-        <v>6949917</v>
+        <v>6950264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1881,17 +1871,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,6 +1897,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1911,21 +1911,21 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128156516</v>
+        <v>128156494</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483708</v>
+        <v>483844</v>
       </c>
       <c r="R14" t="n">
-        <v>6949974</v>
+        <v>6949850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128156511</v>
+        <v>128156495</v>
       </c>
       <c r="B15" t="n">
-        <v>80160</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483692</v>
+        <v>483870</v>
       </c>
       <c r="R15" t="n">
-        <v>6949854</v>
+        <v>6949710</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2099,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,10 +2134,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128156506</v>
+        <v>128156496</v>
       </c>
       <c r="B16" t="n">
-        <v>81074</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2145,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483764</v>
+        <v>483718</v>
       </c>
       <c r="R16" t="n">
-        <v>6949936</v>
+        <v>6949925</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2205,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran bredvid asp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128156504</v>
+        <v>128156499</v>
       </c>
       <c r="B17" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483690</v>
+        <v>483706</v>
       </c>
       <c r="R17" t="n">
-        <v>6949852</v>
+        <v>6949897</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,11 +2311,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2336,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128156496</v>
+        <v>128156504</v>
       </c>
       <c r="B18" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483718</v>
+        <v>483690</v>
       </c>
       <c r="R18" t="n">
-        <v>6949925</v>
+        <v>6949852</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,7 +2416,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran bredvid asp.</t>
+          <t>På grov asp.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2442,10 +2447,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128156515</v>
+        <v>128156509</v>
       </c>
       <c r="B19" t="n">
-        <v>80195</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,21 +2458,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2482,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483695</v>
+        <v>483701</v>
       </c>
       <c r="R19" t="n">
-        <v>6949873</v>
+        <v>6949917</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,6 +2518,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128156499</v>
+        <v>128156514</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,10 +2588,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483706</v>
+        <v>483829</v>
       </c>
       <c r="R20" t="n">
-        <v>6949897</v>
+        <v>6949915</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2644,10 +2654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128156517</v>
+        <v>128156516</v>
       </c>
       <c r="B21" t="n">
-        <v>80195</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,21 +2665,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2750,32 +2760,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128156510</v>
+        <v>128156501</v>
       </c>
       <c r="B22" t="n">
-        <v>81074</v>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483849</v>
+        <v>483832</v>
       </c>
       <c r="R22" t="n">
-        <v>6949856</v>
+        <v>6949887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2844,6 +2854,435 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128156508</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>483701</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6949917</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Pär Hedberg, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>103968181</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skäftesmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>483565</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6950269</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128156503</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>483690</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6949852</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På grov asp.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Pär Hedberg, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128156511</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>483692</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6949854</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pär Hedberg, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>

--- a/artfynd/A 7483-2023 artfynd.xlsx
+++ b/artfynd/A 7483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156506</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156513</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156498</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156507</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156515</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156517</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156505</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156502</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156512</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968142</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156494</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2131,6 +2201,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156495</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156496</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2338,6 +2418,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156499</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2444,6 +2529,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156504</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2550,6 +2640,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156509</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2651,6 +2746,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156514</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2757,6 +2857,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156516</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2858,6 +2963,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156501</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2964,6 +3074,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156508</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3080,6 +3195,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968181</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3186,6 +3306,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156503</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3287,8 +3412,40 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128156511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>